--- a/Unjumble Game 피드백.xlsx
+++ b/Unjumble Game 피드백.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\Unjumble-Game\Unjumble-Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25296F8-1069-4BDF-A669-8D2BC2D8C7C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167AE16F-0911-4171-B7C6-AD88A84FE5DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8050" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_전체 의견" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="사용된단어" sheetId="10" state="hidden" r:id="rId3"/>
     <sheet name="사용된문장" sheetId="11" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -168,14 +168,6 @@
     <t>배경음악(무료)</t>
   </si>
   <si>
-    <t>How to Play 클릭 후 하단에 Game Start 누르면 첫 페이지로 가는데 단어 고르기 화면으로 가도록 하는게 좋을것 같아요.</t>
-  </si>
-  <si>
-    <t>정답 팝업을 ✕로 닫으면 게임이 멈춰 더 진행할 수 없습니다
-문장을 맞히면 축하 팝업이 뜨고, 다음 문제로 가는 유일한 방법이 그 팝업 안의 '다음 문제 ➜' 버튼입니다. 그런데 팝업 우측 상단의 ✕를 누르면 팝업만 사라지고 다음 문제로 갈 수단이 아무것도 남지 않습니다. 이때 제출·힌트·다시 섞기 버튼은 눌리기는 하지만 아무 반응이 없어, 학생은 게임을 버리고 처음으로 돌아가는 수밖에 없습니다. 3번 틀려 정답이 공개된 경우에도 동일합니다.
-→ ✕로 닫을 때도 다음 문제로 넘어가도록 하거나, 이미 답한 문제에서는 ✕ 버튼을 감춰 주세요.</t>
-  </si>
-  <si>
     <t xml:space="preserve">문장 수정
 Let us study English together. -&gt; Let's study English together.로 수정
 Let us가 원형이기는 하나 어색합니다. </t>
@@ -793,9 +785,6 @@
     <t>4. They ride the train together.</t>
   </si>
   <si>
-    <t>그들은 함께 기차를 타요.</t>
-  </si>
-  <si>
     <t>3. It's raining a lot</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -805,22 +794,6 @@
   </si>
   <si>
     <r>
-      <t>사용된</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 문장' 탭을 확인하여 반영</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>안녕</t>
     </r>
     <r>
@@ -2434,6 +2407,1998 @@
   </si>
   <si>
     <t>첫화면 표지는 화면에 꽉 차게 해줘.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그들은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기차를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용된 문장' 탭을 확인하여 반영</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">How to Play </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하단에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Game Start </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누르면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>첫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가는데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고르기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋을것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>닫으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멈춰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진행할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없습니다
+문장을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞히면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>축하</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뜨고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유일한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방법이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>➜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버튼입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상단의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누르면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사라지고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수단이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제출</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힌트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>섞기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버튼은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눌리기는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반응이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>학생은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌아가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수밖에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>틀려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정답이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공개된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경우에도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+→ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>닫을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넘어가도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하거나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>답한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제에서는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버튼을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감춰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -2444,7 +4409,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2608,6 +4573,12 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2668,7 +4639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2742,16 +4713,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3154,7 +5128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -3294,15 +5268,15 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="41"/>
-      <c r="B13" s="43" t="s">
+      <c r="A13" s="44"/>
+      <c r="B13" s="46" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
       <c r="C14" s="2" t="s">
         <v>30</v>
       </c>
@@ -3310,33 +5284,33 @@
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A15" s="42"/>
-      <c r="B15" s="43" t="s">
+      <c r="A15" s="45"/>
+      <c r="B15" s="46" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="34"/>
       <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="42"/>
-      <c r="B17" s="43" t="s">
+      <c r="A17" s="45"/>
+      <c r="B17" s="46" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="42"/>
-      <c r="B18" s="42"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="45"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="42"/>
-      <c r="B19" s="43" t="s">
+      <c r="A19" s="45"/>
+      <c r="B19" s="46" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -3344,22 +5318,22 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="45"/>
       <c r="C20" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
       <c r="C21" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="42"/>
-      <c r="B22" s="42"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
       <c r="C22" s="2" t="s">
         <v>36</v>
       </c>
@@ -3376,14 +5350,14 @@
     </row>
     <row r="24" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="B24" s="4"/>
-      <c r="C24" s="45" t="s">
-        <v>308</v>
+      <c r="C24" s="42" t="s">
+        <v>304</v>
       </c>
       <c r="E24" s="24"/>
     </row>
     <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.45">
-      <c r="C25" s="46" t="s">
-        <v>309</v>
+      <c r="C25" s="43" t="s">
+        <v>305</v>
       </c>
       <c r="E25" s="24"/>
     </row>
@@ -6297,11 +8271,12 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
   <drawing r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6331,8 +8306,8 @@
       <c r="A2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>307</v>
+      <c r="B2" s="41" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.45">
@@ -6340,23 +8315,23 @@
         <v>24</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="47" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="156.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>46</v>
+      <c r="B5" s="34" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="225" customHeight="1" x14ac:dyDescent="0.25">
@@ -6364,7 +8339,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="144" customHeight="1" x14ac:dyDescent="0.25">
@@ -6372,7 +8347,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="144" customHeight="1" x14ac:dyDescent="0.25">
@@ -6380,7 +8355,7 @@
         <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="203.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -6388,7 +8363,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="112.5" x14ac:dyDescent="0.25">
@@ -6396,7 +8371,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="100" x14ac:dyDescent="0.25">
@@ -6404,13 +8379,13 @@
         <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="A12" s="22"/>
       <c r="B12" s="34" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
@@ -9407,6 +11382,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -9438,1266 +11414,1266 @@
     <row r="2" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="36" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="36" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="36" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="37" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="36" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="36" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="36" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="29" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="36" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="36" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B26" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B27" s="36" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B28" s="29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B29" s="36" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B30" s="30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B31" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B32" s="30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B33" s="38" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B34" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B35" s="38" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B36" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B37" s="38" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B38" s="30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B39" s="38" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B40" s="30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B41" s="30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B42" s="38" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B43" s="30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B44" s="38" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B45" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B46" s="38" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B47" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B48" s="39" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B49" s="30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B50" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B51" s="38" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B52" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B53" s="30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B54" s="30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B55" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B56" s="30" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B57" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B58" s="30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B59" s="30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B60" s="30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B61" s="30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B62" s="30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B63" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B64" s="30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B65" s="30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B66" s="30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B67" s="30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B68" s="30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B69" s="30" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B70" s="30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B71" s="30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B72" s="30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B73" s="30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B74" s="30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B75" s="30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B76" s="40" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B77" s="30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B78" s="30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B79" s="40" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="80" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B80" s="32" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B81" s="30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B82" s="30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B83" s="40" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B84" s="32" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B85" s="30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B86" s="30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B87" s="30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B88" s="30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B89" s="30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B90" s="30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B91" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="92" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B92" s="30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B93" s="30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B94" s="30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B95" s="40" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="96" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B96" s="30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B97" s="30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B98" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B99" s="30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B100" s="30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B101" s="30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B102" s="30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B103" s="32" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C103" s="31"/>
     </row>
     <row r="104" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B104" s="30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B105" s="30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B106" s="30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B107" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B108" s="30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B109" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B110" s="30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B111" s="30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B112" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B113" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B114" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="115" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B115" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B116" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B117" s="30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B118" s="30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B119" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="120" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B120" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B121" s="30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B122" s="30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="123" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B123" s="30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="124" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B124" s="30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B125" s="30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B126" s="38" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="127" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B127" s="30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B128" s="30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="129" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B129" s="30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B130" s="30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="131" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B131" s="30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="132" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B132" s="30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B133" s="30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="134" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B134" s="30" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B135" s="38" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B136" s="32" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B137" s="40" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="138" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B138" s="30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="139" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B139" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="140" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B140" s="30" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="141" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B141" s="30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="142" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B142" s="30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="143" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B143" s="30" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="144" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B144" s="30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B145" s="38" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="146" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B146" s="30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="147" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B147" s="38" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B148" s="30" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="149" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B149" s="30" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="150" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B150" s="30" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="151" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B151" s="30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="152" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B152" s="30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B153" s="30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="154" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B154" s="38" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="155" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B155" s="32" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="156" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B156" s="38" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="157" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B157" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="158" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B158" s="30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="159" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B159" s="32" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B160" s="38" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="161" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B161" s="30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="162" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B162" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="163" spans="2:3" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B163" s="38" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="164" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B164" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="165" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B165" s="30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="166" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B166" s="30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="167" spans="2:3" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B167" s="38" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="168" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B168" s="30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B169" s="30" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="170" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B170" s="30" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="171" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B171" s="30" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B172" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="173" spans="2:3" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B173" s="38" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="174" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B174" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="175" spans="2:3" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B175" s="38" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="176" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B176" s="32" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C176" s="31"/>
     </row>
     <row r="177" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B177" s="30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B178" s="30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B179" s="30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B180" s="30" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B181" s="30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="182" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B182" s="30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B183" s="30" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B184" s="40" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="185" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B185" s="30" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="186" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B186" s="30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B187" s="32" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="188" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B188" s="30" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B189" s="30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B190" s="30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="191" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B191" s="30" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B192" s="30" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B193" s="30" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="194" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B194" s="30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="195" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B195" s="30" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="196" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B196" s="30" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B197" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="198" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B198" s="30" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="199" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B199" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="200" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B200" s="30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="201" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B201" s="40" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="202" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B202" s="30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="203" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B203" s="30" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="204" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B204" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="205" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B205" s="30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="206" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B206" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="207" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B207" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="208" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B208" s="30" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="209" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B209" s="32" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="210" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B210" s="38" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="211" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B211" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="212" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B212" s="30" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B213" s="30" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="214" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B214" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="215" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B215" s="30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="216" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B216" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="217" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B217" s="30" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="218" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B218" s="30" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="219" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B219" s="30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="220" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B220" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="221" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B221" s="38" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="222" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B222" s="30" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="223" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B223" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="224" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B224" s="30" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="225" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B225" s="30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="226" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B226" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="227" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B227" s="30" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="228" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B228" s="30" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="229" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B229" s="40" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="230" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B230" s="30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="231" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B231" s="30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="232" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B232" s="30" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="233" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B233" s="30" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="234" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B234" s="30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="235" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B235" s="30" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="236" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B236" s="30" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="237" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B237" s="30" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="238" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
       <c r="B238" s="40" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="239" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B239" s="30" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="240" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B240" s="30" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="241" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B241" s="30" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="242" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B242" s="30" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="243" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B243" s="30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="244" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B244" s="30" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="245" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B245" s="30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="246" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B246" s="30" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="247" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B247" s="30" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="248" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B248" s="30" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="249" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B249" s="30" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="250" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B250" s="30" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B251" s="30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="252" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B252" s="30" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="253" spans="2:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B253" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="B253" s="40" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
